--- a/main/ig/oid2uri-ans.xlsx
+++ b/main/ig/oid2uri-ans.xlsx
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -111,7 +111,7 @@
     <t/>
   </si>
   <si>
-    <t>uri</t>
+    <t>uri|4.0.1</t>
   </si>
   <si>
     <t>1.2.250.1.213.1.1.4.5</t>
